--- a/MI_scen1_calculations.xlsx
+++ b/MI_scen1_calculations.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emilnygaardeik/Documents/Industrial_Ecology/V_2026/MFA2/Project/TEP4290-project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7767ba86a98102bc/TEP4290/Project/TEP4290-project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7E5EDBA-60E8-E443-AFB5-ACFC24C8BD58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{A7E5EDBA-60E8-E443-AFB5-ACFC24C8BD58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9277877-B8C4-4886-BCE9-1A2526F7E59D}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{C721BC97-D025-1F49-9F9A-FF54A8AB1673}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="14235" xr2:uid="{C721BC97-D025-1F49-9F9A-FF54A8AB1673}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -127,9 +127,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="169" formatCode="0.0000"/>
-    <numFmt numFmtId="170" formatCode="0.000"/>
-    <numFmt numFmtId="171" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -146,12 +146,24 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="4">
@@ -201,20 +213,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -230,6 +244,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -550,19 +568,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{210FCC02-B2ED-C043-8F1B-4A3A7A1AD155}">
   <dimension ref="A1:V22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="10" max="10" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.6875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.6875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.6875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.6875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.6875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.6875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.6875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.5">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -624,7 +642,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.5">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -702,7 +720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.5">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -740,7 +758,7 @@
         <v>0.51679817782477833</v>
       </c>
       <c r="L3" s="3">
-        <f t="shared" ref="K3:P3" si="2">D3/$I$3</f>
+        <f t="shared" ref="L3:P3" si="2">D3/$I$3</f>
         <v>4.3927438379565607E-2</v>
       </c>
       <c r="M3" s="3">
@@ -780,7 +798,7 @@
         <v>0.14754098360655737</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.5">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -842,7 +860,7 @@
         <v>76.599999999999994</v>
       </c>
       <c r="S4" s="4">
-        <f t="shared" ref="S3:S5" si="8">E4/R4</f>
+        <f t="shared" ref="S4:S5" si="8">E4/R4</f>
         <v>0.92036553524804188</v>
       </c>
       <c r="T4" s="4">
@@ -858,7 +876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.5">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -887,23 +905,23 @@
         <f t="shared" si="1"/>
         <v>1233.7</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="8">
         <f>B5/$I$5</f>
         <v>0.62657047904676988</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="8">
         <f t="shared" ref="K5:P5" si="9">C5/$I$5</f>
         <v>0.31660857582880764</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="8">
         <f t="shared" si="9"/>
         <v>1.7751479289940825E-2</v>
       </c>
-      <c r="M5" s="3">
+      <c r="M5" s="8">
         <f t="shared" si="9"/>
         <v>3.4124989867877119E-2</v>
       </c>
-      <c r="N5" s="3">
+      <c r="N5" s="8">
         <f t="shared" si="9"/>
         <v>2.4317094917727161E-3</v>
       </c>
@@ -936,12 +954,12 @@
         <v>4.1493775933609959E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.5">
       <c r="A9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.5">
       <c r="B10" s="1" t="s">
         <v>0</v>
       </c>
@@ -967,21 +985,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.5">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B11">
         <f>I2*$B$21</f>
-        <v>360.94</v>
+        <v>812.1149999999999</v>
       </c>
       <c r="C11">
         <f>I2*$B$20</f>
-        <v>360.94</v>
+        <v>451.17499999999995</v>
       </c>
       <c r="D11">
         <f>I2*$B$19</f>
-        <v>992.58500000000004</v>
+        <v>451.17499999999995</v>
       </c>
       <c r="E11">
         <f>I2*$B$22*S2</f>
@@ -1001,24 +1019,24 @@
       </c>
       <c r="I11">
         <f>SUM(B11:H11)</f>
-        <v>1804.7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+        <v>1804.6999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.5">
       <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B12">
         <f t="shared" ref="B12:B14" si="10">I3*$B$21</f>
-        <v>245.86</v>
+        <v>553.18499999999995</v>
       </c>
       <c r="C12">
         <f t="shared" ref="C12:C14" si="11">I3*$B$20</f>
-        <v>245.86</v>
+        <v>307.32499999999999</v>
       </c>
       <c r="D12">
         <f t="shared" ref="D12:D14" si="12">I3*$B$19</f>
-        <v>676.11500000000001</v>
+        <v>307.32499999999999</v>
       </c>
       <c r="E12">
         <f>I3*$B$22*S3</f>
@@ -1041,24 +1059,24 @@
         <v>1229.3000000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.5">
       <c r="A13" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B13">
         <f t="shared" si="10"/>
-        <v>360.94</v>
+        <v>812.1149999999999</v>
       </c>
       <c r="C13">
         <f t="shared" si="11"/>
-        <v>360.94</v>
+        <v>451.17499999999995</v>
       </c>
       <c r="D13">
         <f t="shared" si="12"/>
-        <v>992.58500000000004</v>
+        <v>451.17499999999995</v>
       </c>
       <c r="E13">
-        <f t="shared" ref="E12:E14" si="17">I4*$B$22*S4</f>
+        <f t="shared" ref="E13:E14" si="17">I4*$B$22*S4</f>
         <v>83.049184073107057</v>
       </c>
       <c r="F13">
@@ -1075,71 +1093,71 @@
       </c>
       <c r="I13">
         <f t="shared" si="16"/>
-        <v>1804.7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+        <v>1804.6999999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.5">
       <c r="A14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="7">
         <f t="shared" si="10"/>
-        <v>246.74</v>
-      </c>
-      <c r="C14">
+        <v>555.16500000000008</v>
+      </c>
+      <c r="C14" s="7">
         <f t="shared" si="11"/>
-        <v>246.74</v>
-      </c>
-      <c r="D14">
+        <v>308.42500000000001</v>
+      </c>
+      <c r="D14" s="7">
         <f t="shared" si="12"/>
-        <v>678.53500000000008</v>
-      </c>
-      <c r="E14">
+        <v>308.42500000000001</v>
+      </c>
+      <c r="E14" s="7">
         <f t="shared" si="17"/>
         <v>53.878392116182575</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="7">
         <f t="shared" si="13"/>
         <v>3.8393153526970951</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="7">
         <f t="shared" si="14"/>
         <v>3.7113381742738589</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="7">
         <f t="shared" si="15"/>
         <v>0.25595435684647305</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="7">
         <f t="shared" si="16"/>
         <v>1233.6999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A19" t="s">
         <v>20</v>
       </c>
       <c r="B19">
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A20" t="s">
         <v>21</v>
       </c>
       <c r="B20">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A21" t="s">
         <v>12</v>
       </c>
       <c r="B21">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A22" t="s">
         <v>22</v>
       </c>

--- a/MI_scen1_calculations.xlsx
+++ b/MI_scen1_calculations.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7767ba86a98102bc/TEP4290/Project/TEP4290-project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{A7E5EDBA-60E8-E443-AFB5-ACFC24C8BD58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9277877-B8C4-4886-BCE9-1A2526F7E59D}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{A7E5EDBA-60E8-E443-AFB5-ACFC24C8BD58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A55E35C9-C495-4289-8C4D-2A4B5640F87A}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="14235" xr2:uid="{C721BC97-D025-1F49-9F9A-FF54A8AB1673}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="29">
   <si>
     <t>concrete</t>
   </si>
@@ -120,6 +120,9 @@
   </si>
   <si>
     <t>Ratio copper/rest</t>
+  </si>
+  <si>
+    <t>hva faen?</t>
   </si>
 </sst>
 </file>
@@ -161,7 +164,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -213,7 +216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -228,6 +231,7 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -244,10 +248,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -567,7 +567,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{210FCC02-B2ED-C043-8F1B-4A3A7A1AD155}">
-  <dimension ref="A1:V22"/>
+  <dimension ref="A1:V24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="10" max="10" width="11.6875" bestFit="1" customWidth="1"/>
@@ -954,6 +954,42 @@
         <v>4.1493775933609959E-3</v>
       </c>
     </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.5">
+      <c r="J6" s="9">
+        <f>AVERAGE(J2:J5)</f>
+        <v>0.53512742798078039</v>
+      </c>
+      <c r="K6" s="9">
+        <f t="shared" ref="K6:N6" si="10">AVERAGE(K2:K5)</f>
+        <v>0.40043347485989733</v>
+      </c>
+      <c r="L6" s="9">
+        <f t="shared" si="10"/>
+        <v>2.1043932886097173E-2</v>
+      </c>
+      <c r="M6" s="9">
+        <f t="shared" si="10"/>
+        <v>3.7825232683792273E-2</v>
+      </c>
+      <c r="N6" s="3">
+        <f t="shared" si="10"/>
+        <v>2.1505857815614276E-3</v>
+      </c>
+      <c r="O6" s="3">
+        <f t="shared" ref="O6" si="11">AVERAGE(O2:O5)</f>
+        <v>1.5485073838600446E-3</v>
+      </c>
+      <c r="P6" s="3">
+        <f t="shared" ref="P6" si="12">AVERAGE(P2:P5)</f>
+        <v>1.8708384240114456E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.5">
+      <c r="M7" s="3">
+        <f>AVERAGE(M6:P6)</f>
+        <v>1.0848791068306298E-2</v>
+      </c>
+    </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.5">
       <c r="A9" t="s">
         <v>19</v>
@@ -1027,15 +1063,15 @@
         <v>8</v>
       </c>
       <c r="B12">
-        <f t="shared" ref="B12:B14" si="10">I3*$B$21</f>
+        <f t="shared" ref="B12:B14" si="13">I3*$B$21</f>
         <v>553.18499999999995</v>
       </c>
       <c r="C12">
-        <f t="shared" ref="C12:C14" si="11">I3*$B$20</f>
+        <f t="shared" ref="C12:C14" si="14">I3*$B$20</f>
         <v>307.32499999999999</v>
       </c>
       <c r="D12">
-        <f t="shared" ref="D12:D14" si="12">I3*$B$19</f>
+        <f t="shared" ref="D12:D14" si="15">I3*$B$19</f>
         <v>307.32499999999999</v>
       </c>
       <c r="E12">
@@ -1043,19 +1079,19 @@
         <v>48.365901639344266</v>
       </c>
       <c r="F12">
-        <f t="shared" ref="F12:F14" si="13">I3*$B$22*T3</f>
+        <f t="shared" ref="F12:F14" si="16">I3*$B$22*T3</f>
         <v>2.0152459016393447</v>
       </c>
       <c r="G12">
-        <f t="shared" ref="G12:G14" si="14">I3*$B$22*U3</f>
+        <f t="shared" ref="G12:G14" si="17">I3*$B$22*U3</f>
         <v>2.0152459016393447</v>
       </c>
       <c r="H12">
-        <f t="shared" ref="H12:H14" si="15">I3*$B$22*V3</f>
+        <f t="shared" ref="H12:H14" si="18">I3*$B$22*V3</f>
         <v>9.0686065573770502</v>
       </c>
       <c r="I12">
-        <f t="shared" ref="I12:I14" si="16">SUM(B12:H12)</f>
+        <f t="shared" ref="I12:I14" si="19">SUM(B12:H12)</f>
         <v>1229.3000000000002</v>
       </c>
     </row>
@@ -1064,35 +1100,35 @@
         <v>9</v>
       </c>
       <c r="B13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>812.1149999999999</v>
       </c>
       <c r="C13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>451.17499999999995</v>
       </c>
       <c r="D13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>451.17499999999995</v>
       </c>
       <c r="E13">
-        <f t="shared" ref="E13:E14" si="17">I4*$B$22*S4</f>
+        <f t="shared" ref="E13:E14" si="20">I4*$B$22*S4</f>
         <v>83.049184073107057</v>
       </c>
       <c r="F13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>4.8298107049608348</v>
       </c>
       <c r="G13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>2.356005221932115</v>
       </c>
       <c r="H13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="I13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>1804.6999999999998</v>
       </c>
     </row>
@@ -1101,35 +1137,35 @@
         <v>10</v>
       </c>
       <c r="B14" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>555.16500000000008</v>
       </c>
       <c r="C14" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>308.42500000000001</v>
       </c>
       <c r="D14" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>308.42500000000001</v>
       </c>
       <c r="E14" s="7">
+        <f t="shared" si="20"/>
+        <v>53.878392116182575</v>
+      </c>
+      <c r="F14" s="7">
+        <f t="shared" si="16"/>
+        <v>3.8393153526970951</v>
+      </c>
+      <c r="G14" s="7">
         <f t="shared" si="17"/>
-        <v>53.878392116182575</v>
-      </c>
-      <c r="F14" s="7">
-        <f t="shared" si="13"/>
-        <v>3.8393153526970951</v>
-      </c>
-      <c r="G14" s="7">
-        <f t="shared" si="14"/>
         <v>3.7113381742738589</v>
       </c>
       <c r="H14" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0.25595435684647305</v>
       </c>
       <c r="I14" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>1233.6999999999998</v>
       </c>
     </row>
@@ -1163,6 +1199,11 @@
       </c>
       <c r="B22">
         <v>0.05</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A24" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
